--- a/ARM Functions/Ability Edits/Rivalry.xlsx
+++ b/ARM Functions/Ability Edits/Rivalry.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Ability Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E22CBB-68FD-45C2-BA8E-488FC7BB32E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60CAA1DB-ACB5-4116-B4B6-59EDFF662D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{B6A17A7B-8C08-4586-ACA6-4708B18997FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Rivalry" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateCount="5"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -71,9 +71,6 @@
     <t>move max HP into r1</t>
   </si>
   <si>
-    <t>bl #0x92628</t>
-  </si>
-  <si>
     <t>mov r0, r4</t>
   </si>
   <si>
@@ -83,27 +80,18 @@
     <t>FDFFFFEA</t>
   </si>
   <si>
-    <t>mov r1, #0x0E</t>
-  </si>
-  <si>
     <t>0E10A0E3</t>
   </si>
   <si>
     <t>0D10A0E3</t>
   </si>
   <si>
-    <t>bl #0x92298</t>
-  </si>
-  <si>
     <t>mov r0, r5</t>
   </si>
   <si>
     <t>0500A0E1</t>
   </si>
   <si>
-    <t>bl #0x87b58</t>
-  </si>
-  <si>
     <t>0400A0E3</t>
   </si>
   <si>
@@ -131,9 +119,6 @@
     <t>Attacker</t>
   </si>
   <si>
-    <t>mov r0, #3</t>
-  </si>
-  <si>
     <t>0300A0E3</t>
   </si>
   <si>
@@ -282,6 +267,21 @@
   </si>
   <si>
     <t>F8B0FEEA</t>
+  </si>
+  <si>
+    <t>bl 0x00087B58</t>
+  </si>
+  <si>
+    <t>bl 0x00092298</t>
+  </si>
+  <si>
+    <t>bl 0x00092628</t>
+  </si>
+  <si>
+    <t>mov r1, 0x0E</t>
+  </si>
+  <si>
+    <t>mov r0, 0x3</t>
   </si>
 </sst>
 </file>
@@ -365,7 +365,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -388,7 +388,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -737,21 +736,21 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -759,13 +758,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -774,10 +773,10 @@
         <v>000D6CA0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -786,10 +785,10 @@
         <v>000D6CA4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -798,13 +797,13 @@
         <v>000D6CA8</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -813,10 +812,10 @@
         <v>000D6CAC</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="D7" s="4"/>
     </row>
@@ -826,10 +825,10 @@
         <v>000D6CB0</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6"/>
@@ -841,13 +840,13 @@
         <v>000D6CB4</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
@@ -858,14 +857,14 @@
         <v>000D6CB8</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C10" s="8" t="str">
         <f>_xlfn.CONCAT("beq 0x",A$16)</f>
         <v>beq 0x000D6CD0</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -876,13 +875,13 @@
         <v>000D6CBC</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -893,10 +892,10 @@
         <v>000D6CC0</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="6"/>
@@ -908,10 +907,10 @@
         <v>000D6CC4</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="6"/>
@@ -923,7 +922,7 @@
         <v>000D6CC8</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C14" s="9" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$37)</f>
@@ -938,13 +937,13 @@
         <v>000D6CCC</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -955,13 +954,13 @@
         <v>000D6CD0</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -970,10 +969,10 @@
         <v>000D6CD4</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D17" s="12"/>
     </row>
@@ -983,10 +982,10 @@
         <v>000D6CD8</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="D18" s="12"/>
     </row>
@@ -996,10 +995,10 @@
         <v>000D6CDC</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D19" s="12"/>
     </row>
@@ -1009,10 +1008,10 @@
         <v>000D6CE0</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D20" s="17"/>
     </row>
@@ -1022,10 +1021,10 @@
         <v>000D6CE4</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D21" s="17"/>
       <c r="E21" s="18"/>
@@ -1036,10 +1035,10 @@
         <v>000D6CE8</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="D22" s="15"/>
     </row>
@@ -1049,13 +1048,13 @@
         <v>000D6CEC</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C23" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="15" t="s">
         <v>43</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>48</v>
       </c>
       <c r="E23" s="18"/>
       <c r="F23" s="18"/>
@@ -1066,10 +1065,10 @@
         <v>000D6CF0</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="D24" s="19"/>
     </row>
@@ -1079,10 +1078,10 @@
         <v>000D6CF4</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D25" s="19"/>
       <c r="G25" s="2" t="s">
@@ -1095,20 +1094,20 @@
         <v>000D6CF8</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="22" t="str">
+      <c r="A27" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D6CFC</v>
       </c>
@@ -1123,15 +1122,15 @@
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="22" t="str">
+      <c r="A28" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000D6D00</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>9</v>
@@ -1149,7 +1148,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1158,13 +1157,13 @@
         <v>000D6D08</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1173,10 +1172,10 @@
         <v>000D6D0C</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1185,13 +1184,13 @@
         <v>000D6D10</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1200,13 +1199,13 @@
         <v>000D6D14</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1227,7 +1226,7 @@
         <v>000D6D1C</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C35" s="2" t="str">
         <f>SUBSTITUTE(C3,"push","pop")</f>
@@ -1240,7 +1239,7 @@
         <v>000D6D20</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>1</v>
@@ -1252,7 +1251,7 @@
         <v>000D6D24</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C37" s="2" t="str">
         <f>SUBSTITUTE(C35,"lr","pc")</f>
